--- a/per-stock/P/financials.xlsx
+++ b/per-stock/P/financials.xlsx
@@ -1,19 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (annual)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Income stmt (quarterly)" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet (annual)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (annual)" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data flags" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="FY Summary" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Income stmt (annual)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Income stmt (quarterly)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Balance sheet (annual)" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Balance sheet (quarterly)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Cash flow (annual)" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Cash flow (quarterly)" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Data flags" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +24,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="3">
+    <numFmt numFmtId="164" formatCode="0.0%"/>
+    <numFmt numFmtId="165" formatCode="0.00&quot;x&quot;"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -61,11 +67,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -464,7 +473,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>PSTG</t>
+          <t>P</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -481,7 +490,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Everpure Inc</t>
+          <t>Everpure, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -531,7 +540,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22405251072</v>
+        <v>24800731136</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -546,7 +555,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21808037888</v>
+        <v>24332759040</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -561,7 +570,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>123.27273</v>
+        <v>113.04545</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -576,7 +585,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23.884089</v>
+        <v>24.801712</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -591,7 +600,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6.116902</v>
+        <v>6.298992</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -606,7 +615,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.70381</v>
+        <v>0.7023</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -636,7 +645,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.05138</v>
+        <v>0.05746</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -651,7 +660,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.13675</v>
+        <v>0.16846001</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -713,11 +722,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>376732640</v>
+        <v>515901000</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>yfinance info.freeCashflow</t>
+          <t>statement: TTM OCF - |capex| (yfinance quarterly_cashflow)</t>
         </is>
       </c>
     </row>
@@ -728,7 +737,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>330460930</v>
+        <v>332404932</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -743,7 +752,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>67.8</v>
+        <v>74.61</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -787,6 +796,477 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="52" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fiscal-year summary (GAAP, $ except where noted)</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>FY-3</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>FY-2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>FY-1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TTM</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Source / formula</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Fiscal period end</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2024-01-31</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>TTM → 2026-04-30</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>annual statement headers; TTM = Σ last 4 quarters</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B3" s="3">
+        <f>'Income stmt (annual)'!D50</f>
+        <v/>
+      </c>
+      <c r="C3" s="3">
+        <f>'Income stmt (annual)'!C50</f>
+        <v/>
+      </c>
+      <c r="D3" s="3">
+        <f>'Income stmt (annual)'!B50</f>
+        <v/>
+      </c>
+      <c r="E3" s="3">
+        <f>SUM('Income stmt (quarterly)'!B46:E46)</f>
+        <v/>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Total Revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B4" s="3">
+        <f>'Income stmt (annual)'!D48</f>
+        <v/>
+      </c>
+      <c r="C4" s="3">
+        <f>'Income stmt (annual)'!C48</f>
+        <v/>
+      </c>
+      <c r="D4" s="3">
+        <f>'Income stmt (annual)'!B48</f>
+        <v/>
+      </c>
+      <c r="E4" s="3">
+        <f>SUM('Income stmt (quarterly)'!B44:E44)</f>
+        <v/>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Gross Profit (GAAP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Gross margin %</t>
+        </is>
+      </c>
+      <c r="B5" s="4">
+        <f>IFERROR(B4/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C5" s="4">
+        <f>IFERROR(C4/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D5" s="4">
+        <f>IFERROR(D4/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E5" s="4">
+        <f>IFERROR(E4/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>GAAP = gross profit / revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Operating income</t>
+        </is>
+      </c>
+      <c r="B6" s="3">
+        <f>'Income stmt (annual)'!D40</f>
+        <v/>
+      </c>
+      <c r="C6" s="3">
+        <f>'Income stmt (annual)'!C40</f>
+        <v/>
+      </c>
+      <c r="D6" s="3">
+        <f>'Income stmt (annual)'!B40</f>
+        <v/>
+      </c>
+      <c r="E6" s="3">
+        <f>SUM('Income stmt (quarterly)'!B37:E37)</f>
+        <v/>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Operating Income</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Operating margin %</t>
+        </is>
+      </c>
+      <c r="B7" s="4">
+        <f>IFERROR(B6/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C7" s="4">
+        <f>IFERROR(C6/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D7" s="4">
+        <f>IFERROR(D6/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E7" s="4">
+        <f>IFERROR(E6/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F7">
+        <f> operating income / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B8" s="3">
+        <f>'Income stmt (annual)'!D10</f>
+        <v/>
+      </c>
+      <c r="C8" s="3">
+        <f>'Income stmt (annual)'!C10</f>
+        <v/>
+      </c>
+      <c r="D8" s="3">
+        <f>'Income stmt (annual)'!B10</f>
+        <v/>
+      </c>
+      <c r="E8" s="3">
+        <f>SUM('Income stmt (quarterly)'!B10:E10)</f>
+        <v/>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>EBITDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Free cash flow</t>
+        </is>
+      </c>
+      <c r="B9" s="3">
+        <f>'Cash flow (annual)'!D2</f>
+        <v/>
+      </c>
+      <c r="C9" s="3">
+        <f>'Cash flow (annual)'!C2</f>
+        <v/>
+      </c>
+      <c r="D9" s="3">
+        <f>'Cash flow (annual)'!B2</f>
+        <v/>
+      </c>
+      <c r="E9" s="3">
+        <f>SUM('Cash flow (quarterly)'!B2:E2)</f>
+        <v/>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>FCF = OCF − capex</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FCF margin %</t>
+        </is>
+      </c>
+      <c r="B10" s="4">
+        <f>IFERROR(B9/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C10" s="4">
+        <f>IFERROR(C9/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D10" s="4">
+        <f>IFERROR(D9/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E10" s="4">
+        <f>IFERROR(E9/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F10">
+        <f> FCF / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Capex</t>
+        </is>
+      </c>
+      <c r="B11" s="3">
+        <f>-'Cash flow (annual)'!D6</f>
+        <v/>
+      </c>
+      <c r="C11" s="3">
+        <f>-'Cash flow (annual)'!C6</f>
+        <v/>
+      </c>
+      <c r="D11" s="3">
+        <f>-'Cash flow (annual)'!B6</f>
+        <v/>
+      </c>
+      <c r="E11" s="3">
+        <f>-SUM('Cash flow (quarterly)'!B6:E6)</f>
+        <v/>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Capex (shown positive)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Capex / revenue %</t>
+        </is>
+      </c>
+      <c r="B12" s="4">
+        <f>IFERROR(B11/B3,"")</f>
+        <v/>
+      </c>
+      <c r="C12" s="4">
+        <f>IFERROR(C11/C3,"")</f>
+        <v/>
+      </c>
+      <c r="D12" s="4">
+        <f>IFERROR(D11/D3,"")</f>
+        <v/>
+      </c>
+      <c r="E12" s="4">
+        <f>IFERROR(E11/E3,"")</f>
+        <v/>
+      </c>
+      <c r="F12">
+        <f> capex / revenue</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Net debt</t>
+        </is>
+      </c>
+      <c r="B13" s="3">
+        <f>'Balance sheet (annual)'!D4</f>
+        <v/>
+      </c>
+      <c r="C13" s="3">
+        <f>'Balance sheet (annual)'!C4</f>
+        <v/>
+      </c>
+      <c r="D13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="E13" s="3">
+        <f>'Balance sheet (annual)'!B4</f>
+        <v/>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Net debt; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Net debt / EBITDA</t>
+        </is>
+      </c>
+      <c r="B14" s="5">
+        <f>IFERROR(B13/B8,"")</f>
+        <v/>
+      </c>
+      <c r="C14" s="5">
+        <f>IFERROR(C13/C8,"")</f>
+        <v/>
+      </c>
+      <c r="D14" s="5">
+        <f>IFERROR(D13/D8,"")</f>
+        <v/>
+      </c>
+      <c r="E14" s="5">
+        <f>IFERROR(E13/E8,"")</f>
+        <v/>
+      </c>
+      <c r="F14">
+        <f> net debt / EBITDA</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Share count (period-end, M)</t>
+        </is>
+      </c>
+      <c r="B15" s="6">
+        <f>'Balance sheet (annual)'!D2/1e6</f>
+        <v/>
+      </c>
+      <c r="C15" s="6">
+        <f>'Balance sheet (annual)'!C2/1e6</f>
+        <v/>
+      </c>
+      <c r="D15" s="6">
+        <f>'Balance sheet (annual)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="E15" s="6">
+        <f>'Balance sheet (quarterly)'!B2/1e6</f>
+        <v/>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>shares ÷ 1e6; TTM = MRQ</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Share count YoY %</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="inlineStr"/>
+      <c r="C16" s="4">
+        <f>IFERROR(C15/B15-1,"")</f>
+        <v/>
+      </c>
+      <c r="D16" s="4">
+        <f>IFERROR(D15/C15-1,"")</f>
+        <v/>
+      </c>
+      <c r="E16" s="4">
+        <f>IFERROR(E15/D15-1,"")</f>
+        <v/>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>vs prior period</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1832,13 +2312,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:G47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1847,6 +2327,7 @@
     <col width="16" customWidth="1" min="4" max="4"/>
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1857,25 +2338,30 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
@@ -1888,20 +2374,21 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>-876567.581931</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>372302.92687</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>4238486.820478</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>128981.372723</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>3040590</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>-1493817.767067</v>
-      </c>
+      <c r="G2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1910,20 +2397,21 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>0.289105</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>0.067605</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>0.165916</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>0.06827999999999999</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>0.21</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>0.219357</v>
-      </c>
+      <c r="G3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1932,20 +2420,21 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>77339000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>142597000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>78214000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>85660000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>21582000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>92141000</v>
-      </c>
+      <c r="G4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1954,20 +2443,21 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
+        <v>-3032000</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>5507000</v>
       </c>
-      <c r="C5" s="3" t="n">
+      <c r="D5" s="3" t="n">
         <v>25546000</v>
       </c>
-      <c r="D5" s="3" t="n">
+      <c r="E5" s="3" t="n">
         <v>1889000</v>
       </c>
-      <c r="E5" s="3" t="n">
+      <c r="F5" s="3" t="n">
         <v>14479000</v>
       </c>
-      <c r="F5" s="3" t="n">
-        <v>-6810000</v>
-      </c>
+      <c r="G5" s="3" t="n"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1976,20 +2466,21 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-3032000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>5507000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>25546000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>1889000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>14479000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-6810000</v>
-      </c>
+      <c r="G6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1998,20 +2489,21 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="C7" s="3" t="n">
         <v>100252000</v>
       </c>
-      <c r="C7" s="3" t="n">
+      <c r="D7" s="3" t="n">
         <v>54806000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>47118000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>-13995000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>42435000</v>
-      </c>
+      <c r="G7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2020,20 +2512,21 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>40198000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>40332000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>37786000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>35927000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>33770000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>29125000</v>
-      </c>
+      <c r="G8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2042,20 +2535,21 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>329564000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>318816000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>267076000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>256666000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>242332000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>285841000</v>
-      </c>
+      <c r="G9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -2064,20 +2558,21 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>74307000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>148104000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>103760000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>87549000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>36061000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>85331000</v>
-      </c>
+      <c r="G10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2086,20 +2581,21 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>34109000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>107772000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>65974000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>51622000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>2291000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>56206000</v>
-      </c>
+      <c r="G11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2108,20 +2604,21 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>14065000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>13921000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>15508000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>14614000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>15069000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>15288000</v>
-      </c>
+      <c r="G12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2130,20 +2627,21 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>239000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>251000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>266000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>1051000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>1807000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>1847000</v>
-      </c>
+      <c r="G13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2152,20 +2650,21 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>14304000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>14172000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>15774000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>15665000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>16876000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>17135000</v>
-      </c>
+      <c r="G14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2174,20 +2673,21 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>26233432.418069</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>95117302.92687</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>33498486.820478</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>45357981.372723</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>-25433410</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>47751182.232933</v>
-      </c>
+      <c r="G15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2196,20 +2696,21 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>100252000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>54806000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>47118000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-13995000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>42435000</v>
-      </c>
+      <c r="G16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2218,20 +2719,21 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>1032957000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>971705000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>910535000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>856131000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>809656000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>837375000</v>
-      </c>
+      <c r="G17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2240,20 +2742,21 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>19939000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>87198000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>53918000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>4871000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-31171000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>42467000</v>
-      </c>
+      <c r="G18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2262,20 +2765,21 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>343493000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>346074000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>345747000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>337734000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>326539000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>343109000</v>
-      </c>
+      <c r="G19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2284,20 +2788,21 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>331152000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>330458000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>329570000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>327594000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>326539000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>326504000</v>
-      </c>
+      <c r="G20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2306,20 +2811,21 @@
         </is>
       </c>
       <c r="B21" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C21" s="3" t="n">
         <v>0.29</v>
       </c>
-      <c r="C21" s="3" t="n">
+      <c r="D21" s="3" t="n">
         <v>0.16</v>
       </c>
-      <c r="D21" s="3" t="n">
+      <c r="E21" s="3" t="n">
         <v>0.14</v>
       </c>
-      <c r="E21" s="3" t="n">
+      <c r="F21" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F21" s="3" t="n">
-        <v>0.12</v>
-      </c>
+      <c r="G21" s="3" t="n"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2328,20 +2834,21 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>0.3</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>0.17</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>0.14</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-0.04</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>0.13</v>
-      </c>
+      <c r="G22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2350,20 +2857,21 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>100252000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>54806000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>47118000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-13995000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>42435000</v>
-      </c>
+      <c r="G23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2372,20 +2880,21 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>100252000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>54806000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>47118000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-13995000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>42435000</v>
-      </c>
+      <c r="G24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2394,20 +2903,21 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>100252000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>54806000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>47118000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>-13995000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>42435000</v>
-      </c>
+      <c r="G25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2416,20 +2926,21 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>100252000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>54806000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>47118000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-13995000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>42435000</v>
-      </c>
+      <c r="G26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -2438,20 +2949,21 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="C27" s="3" t="n">
         <v>100252000</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>54806000</v>
       </c>
-      <c r="D27" s="3" t="n">
+      <c r="E27" s="3" t="n">
         <v>47118000</v>
       </c>
-      <c r="E27" s="3" t="n">
+      <c r="F27" s="3" t="n">
         <v>-13995000</v>
       </c>
-      <c r="F27" s="3" t="n">
-        <v>42435000</v>
-      </c>
+      <c r="G27" s="3" t="n"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -2460,20 +2972,21 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
+        <v>9792000</v>
+      </c>
+      <c r="C28" s="3" t="n">
         <v>7269000</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>10902000</v>
       </c>
-      <c r="D28" s="3" t="n">
+      <c r="E28" s="3" t="n">
         <v>3453000</v>
       </c>
-      <c r="E28" s="3" t="n">
+      <c r="F28" s="3" t="n">
         <v>14479000</v>
       </c>
-      <c r="F28" s="3" t="n">
-        <v>11924000</v>
-      </c>
+      <c r="G28" s="3" t="n"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -2482,20 +2995,21 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>33870000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>107521000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>65708000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>50571000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>484000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>54359000</v>
-      </c>
+      <c r="G29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -2504,20 +3018,21 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-134000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>6402000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-3718000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>31086000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>16586000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-3396000</v>
-      </c>
+      <c r="G30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -2526,20 +3041,21 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>2898000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>895000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>-29264000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>29197000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>2107000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>3414000</v>
-      </c>
+      <c r="G31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -2547,9 +3063,7 @@
           <t>Special Income Charges</t>
         </is>
       </c>
-      <c r="B32" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B32" s="3" t="n"/>
       <c r="C32" s="3" t="n">
         <v>0</v>
       </c>
@@ -2562,6 +3076,9 @@
       <c r="F32" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="G32" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -2570,20 +3087,21 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-3032000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>5507000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>25546000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>1889000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>14479000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>-6810000</v>
-      </c>
+      <c r="G33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2592,20 +3110,21 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>14065000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>13921000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>15508000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>14614000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>15069000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>15288000</v>
-      </c>
+      <c r="G34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -2614,20 +3133,21 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>239000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>251000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>266000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>1051000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>1807000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>1847000</v>
-      </c>
+      <c r="G35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -2636,20 +3156,21 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>14304000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>14172000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>15774000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>15665000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>16876000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>17135000</v>
-      </c>
+      <c r="G36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2658,20 +3179,21 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>19939000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>87198000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>53918000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>4871000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-31171000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>42467000</v>
-      </c>
+      <c r="G37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -2680,20 +3202,21 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>703393000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>652889000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>643459000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>599465000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>567324000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>551534000</v>
-      </c>
+      <c r="G38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2702,20 +3225,21 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>259092000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>243161000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>256364000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>242026000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>221740000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>215009000</v>
-      </c>
+      <c r="G39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -2724,20 +3248,21 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>444301000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>409728000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>387095000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>357439000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>345584000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>336525000</v>
-      </c>
+      <c r="G40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -2746,20 +3271,21 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>347856000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>323269000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>293817000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>285890000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>278512000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>263845000</v>
-      </c>
+      <c r="G41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -2768,20 +3294,21 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>96445000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>86459000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>93278000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>71549000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>67072000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>72680000</v>
-      </c>
+      <c r="G42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2790,20 +3317,21 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>96445000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>86459000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>93278000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>71549000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>67072000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>72680000</v>
-      </c>
+      <c r="G43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -2812,20 +3340,21 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>723332000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>740087000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>697377000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>604336000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>536153000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>594001000</v>
-      </c>
+      <c r="G44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2834,20 +3363,21 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>329564000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>318816000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>267076000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>256666000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>242332000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>285841000</v>
-      </c>
+      <c r="G45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2856,20 +3386,21 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>1052896000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>1058903000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>964453000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>861002000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>778485000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>879842000</v>
-      </c>
+      <c r="G46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2878,27 +3409,28 @@
         </is>
       </c>
       <c r="B47" s="3" t="n">
+        <v>1052896000</v>
+      </c>
+      <c r="C47" s="3" t="n">
         <v>1058903000</v>
       </c>
-      <c r="C47" s="3" t="n">
+      <c r="D47" s="3" t="n">
         <v>964453000</v>
       </c>
-      <c r="D47" s="3" t="n">
+      <c r="E47" s="3" t="n">
         <v>861002000</v>
       </c>
-      <c r="E47" s="3" t="n">
+      <c r="F47" s="3" t="n">
         <v>778485000</v>
       </c>
-      <c r="F47" s="3" t="n">
-        <v>879842000</v>
-      </c>
+      <c r="G47" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4344,7 +4876,1689 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H69"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-31</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>2025-10-31</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>2025-07-31</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>2025-04-30</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>2025-01-31</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>2024-10-31</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Ordinary Shares Number</t>
+        </is>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>326938000</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>326102000</v>
+      </c>
+      <c r="D2" s="3" t="n">
+        <v>330509000</v>
+      </c>
+      <c r="E2" s="3" t="n">
+        <v>328315000</v>
+      </c>
+      <c r="F2" s="3" t="n">
+        <v>326938000</v>
+      </c>
+      <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Share Issued</t>
+        </is>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>326938000</v>
+      </c>
+      <c r="C3" s="3" t="n">
+        <v>326102000</v>
+      </c>
+      <c r="D3" s="3" t="n">
+        <v>330509000</v>
+      </c>
+      <c r="E3" s="3" t="n">
+        <v>328315000</v>
+      </c>
+      <c r="F3" s="3" t="n">
+        <v>326938000</v>
+      </c>
+      <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Total Debt</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>230961000</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>216715000</v>
+      </c>
+      <c r="D4" s="3" t="n">
+        <v>226111000</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>223333000</v>
+      </c>
+      <c r="F4" s="3" t="n">
+        <v>271298000</v>
+      </c>
+      <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Tangible Book Value</t>
+        </is>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1071721000</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>1073247000</v>
+      </c>
+      <c r="D5" s="3" t="n">
+        <v>1028740000</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>946251000</v>
+      </c>
+      <c r="F5" s="3" t="n">
+        <v>867520000</v>
+      </c>
+      <c r="G5" s="3" t="n"/>
+      <c r="H5" s="3" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Invested Capital</t>
+        </is>
+      </c>
+      <c r="B6" s="3" t="n">
+        <v>1442138000</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>1445668000</v>
+      </c>
+      <c r="D6" s="3" t="n">
+        <v>1402889000</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>1318821000</v>
+      </c>
+      <c r="F6" s="3" t="n">
+        <v>1344055000</v>
+      </c>
+      <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Working Capital</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="n">
+        <v>1163470000</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1153502000</v>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v>1047231000</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>990330000</v>
+      </c>
+      <c r="F7" s="3" t="n">
+        <v>905716000</v>
+      </c>
+      <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Net Tangible Assets</t>
+        </is>
+      </c>
+      <c r="B8" s="3" t="n">
+        <v>1071721000</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>1073247000</v>
+      </c>
+      <c r="D8" s="3" t="n">
+        <v>1028740000</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>946251000</v>
+      </c>
+      <c r="F8" s="3" t="n">
+        <v>867520000</v>
+      </c>
+      <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Capital Lease Obligations</t>
+        </is>
+      </c>
+      <c r="B9" s="3" t="n">
+        <v>230961000</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>216715000</v>
+      </c>
+      <c r="D9" s="3" t="n">
+        <v>226111000</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>223333000</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>171298000</v>
+      </c>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Common Stock Equity</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="n">
+        <v>1442138000</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>1445668000</v>
+      </c>
+      <c r="D10" s="3" t="n">
+        <v>1402889000</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>1318821000</v>
+      </c>
+      <c r="F10" s="3" t="n">
+        <v>1244055000</v>
+      </c>
+      <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Total Capitalization</t>
+        </is>
+      </c>
+      <c r="B11" s="3" t="n">
+        <v>1442138000</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>1445668000</v>
+      </c>
+      <c r="D11" s="3" t="n">
+        <v>1402889000</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>1318821000</v>
+      </c>
+      <c r="F11" s="3" t="n">
+        <v>1244055000</v>
+      </c>
+      <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Total Equity Gross Minority Interest</t>
+        </is>
+      </c>
+      <c r="B12" s="3" t="n">
+        <v>1442138000</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>1445668000</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>1402889000</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>1318821000</v>
+      </c>
+      <c r="F12" s="3" t="n">
+        <v>1244055000</v>
+      </c>
+      <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Stockholders Equity</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="n">
+        <v>1442138000</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>1445668000</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>1402889000</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>1318821000</v>
+      </c>
+      <c r="F13" s="3" t="n">
+        <v>1244055000</v>
+      </c>
+      <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Gains Losses Not Affecting Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B14" s="3" t="n">
+        <v>-1613000</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>1709000</v>
+      </c>
+      <c r="D14" s="3" t="n">
+        <v>2006000</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>1916000</v>
+      </c>
+      <c r="F14" s="3" t="n">
+        <v>1831000</v>
+      </c>
+      <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Other Equity Adjustments</t>
+        </is>
+      </c>
+      <c r="B15" s="3" t="n">
+        <v>-1613000</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>1709000</v>
+      </c>
+      <c r="D15" s="3" t="n">
+        <v>2006000</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>1916000</v>
+      </c>
+      <c r="F15" s="3" t="n">
+        <v>1831000</v>
+      </c>
+      <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Retained Earnings</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="n">
+        <v>-1156753000</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-1180831000</v>
+      </c>
+      <c r="D16" s="3" t="n">
+        <v>-1281083000</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-1335889000</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>-1383007000</v>
+      </c>
+      <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Additional Paid In Capital</t>
+        </is>
+      </c>
+      <c r="B17" s="3" t="n">
+        <v>2600471000</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>2624757000</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>2681933000</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>2652761000</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>2625198000</v>
+      </c>
+      <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Capital Stock</t>
+        </is>
+      </c>
+      <c r="B18" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C18" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D18" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E18" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F18" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Common Stock</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="C19" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="D19" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="E19" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="F19" s="3" t="n">
+        <v>33000</v>
+      </c>
+      <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Preferred Stock</t>
+        </is>
+      </c>
+      <c r="B20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Total Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B21" s="3" t="n">
+        <v>3307809000</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>3228591000</v>
+      </c>
+      <c r="D21" s="3" t="n">
+        <v>2815522000</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>2707716000</v>
+      </c>
+      <c r="F21" s="3" t="n">
+        <v>2566310000</v>
+      </c>
+      <c r="G21" s="3" t="n"/>
+      <c r="H21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Total Non Current Liabilities Net Minority Interest</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="n">
+        <v>1421398000</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>1318601000</v>
+      </c>
+      <c r="D22" s="3" t="n">
+        <v>1210499000</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>1173308000</v>
+      </c>
+      <c r="F22" s="3" t="n">
+        <v>1071799000</v>
+      </c>
+      <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Other Non Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B23" s="3" t="n">
+        <v>108121000</v>
+      </c>
+      <c r="C23" s="3" t="n">
+        <v>100096000</v>
+      </c>
+      <c r="D23" s="3" t="n">
+        <v>96783000</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>92188000</v>
+      </c>
+      <c r="F23" s="3" t="n">
+        <v>83840000</v>
+      </c>
+      <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B24" s="3" t="n">
+        <v>1127682000</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>1046442000</v>
+      </c>
+      <c r="D24" s="3" t="n">
+        <v>931768000</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>904867000</v>
+      </c>
+      <c r="F24" s="3" t="n">
+        <v>858224000</v>
+      </c>
+      <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B25" s="3" t="n">
+        <v>1127682000</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>1046442000</v>
+      </c>
+      <c r="D25" s="3" t="n">
+        <v>931768000</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>904867000</v>
+      </c>
+      <c r="F25" s="3" t="n">
+        <v>858224000</v>
+      </c>
+      <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Long Term Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B26" s="3" t="n">
+        <v>185595000</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>172063000</v>
+      </c>
+      <c r="D26" s="3" t="n">
+        <v>181948000</v>
+      </c>
+      <c r="E26" s="3" t="n">
+        <v>176253000</v>
+      </c>
+      <c r="F26" s="3" t="n">
+        <v>129735000</v>
+      </c>
+      <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Long Term Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B27" s="3" t="n">
+        <v>185595000</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>172063000</v>
+      </c>
+      <c r="D27" s="3" t="n">
+        <v>181948000</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>176253000</v>
+      </c>
+      <c r="F27" s="3" t="n">
+        <v>129735000</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Current Liabilities</t>
+        </is>
+      </c>
+      <c r="B28" s="3" t="n">
+        <v>1886411000</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>1909990000</v>
+      </c>
+      <c r="D28" s="3" t="n">
+        <v>1605023000</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>1534408000</v>
+      </c>
+      <c r="F28" s="3" t="n">
+        <v>1494511000</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Current Deferred Liabilities</t>
+        </is>
+      </c>
+      <c r="B29" s="3" t="n">
+        <v>1283031000</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>1213960000</v>
+      </c>
+      <c r="D29" s="3" t="n">
+        <v>1057848000</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>1035364000</v>
+      </c>
+      <c r="F29" s="3" t="n">
+        <v>999570000</v>
+      </c>
+      <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Current Deferred Revenue</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="n">
+        <v>1283031000</v>
+      </c>
+      <c r="C30" s="3" t="n">
+        <v>1213960000</v>
+      </c>
+      <c r="D30" s="3" t="n">
+        <v>1057848000</v>
+      </c>
+      <c r="E30" s="3" t="n">
+        <v>1035364000</v>
+      </c>
+      <c r="F30" s="3" t="n">
+        <v>999570000</v>
+      </c>
+      <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Current Debt And Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="n">
+        <v>45366000</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>44652000</v>
+      </c>
+      <c r="D31" s="3" t="n">
+        <v>44163000</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>47080000</v>
+      </c>
+      <c r="F31" s="3" t="n">
+        <v>141563000</v>
+      </c>
+      <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Current Capital Lease Obligation</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="n">
+        <v>45366000</v>
+      </c>
+      <c r="C32" s="3" t="n">
+        <v>44652000</v>
+      </c>
+      <c r="D32" s="3" t="n">
+        <v>44163000</v>
+      </c>
+      <c r="E32" s="3" t="n">
+        <v>47080000</v>
+      </c>
+      <c r="F32" s="3" t="n">
+        <v>41563000</v>
+      </c>
+      <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Current Debt</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="n"/>
+      <c r="C33" s="3" t="n"/>
+      <c r="D33" s="3" t="n"/>
+      <c r="E33" s="3" t="n"/>
+      <c r="F33" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="G33" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="H33" s="3" t="n">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Other Current Borrowings</t>
+        </is>
+      </c>
+      <c r="B34" s="3" t="n"/>
+      <c r="C34" s="3" t="n"/>
+      <c r="D34" s="3" t="n"/>
+      <c r="E34" s="3" t="n"/>
+      <c r="F34" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="G34" s="3" t="n">
+        <v>100000000</v>
+      </c>
+      <c r="H34" s="3" t="n">
+        <v>100000000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Line Of Credit</t>
+        </is>
+      </c>
+      <c r="B35" s="3" t="n"/>
+      <c r="C35" s="3" t="n"/>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n"/>
+      <c r="F35" s="3" t="n"/>
+      <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Pensionand Other Post Retirement Benefit Plans Current</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>236221000</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>347205000</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>244939000</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>212869000</v>
+      </c>
+      <c r="F36" s="3" t="n">
+        <v>142333000</v>
+      </c>
+      <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Payables And Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>321793000</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>304173000</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>258073000</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>239095000</v>
+      </c>
+      <c r="F37" s="3" t="n">
+        <v>211045000</v>
+      </c>
+      <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Current Accrued Expenses</t>
+        </is>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>133594000</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>136817000</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>109768000</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>115758000</v>
+      </c>
+      <c r="F38" s="3" t="n">
+        <v>116211000</v>
+      </c>
+      <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Payables</t>
+        </is>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>188199000</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>167356000</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>148305000</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>123337000</v>
+      </c>
+      <c r="F39" s="3" t="n">
+        <v>94834000</v>
+      </c>
+      <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Total Tax Payable</t>
+        </is>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>14992000</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>14044000</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>20283000</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>11175000</v>
+      </c>
+      <c r="F40" s="3" t="n">
+        <v>10976000</v>
+      </c>
+      <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Accounts Payable</t>
+        </is>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>173207000</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>153312000</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>128022000</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>112162000</v>
+      </c>
+      <c r="F41" s="3" t="n">
+        <v>83858000</v>
+      </c>
+      <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Total Assets</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>4749947000</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>4674259000</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>4218411000</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>4026537000</v>
+      </c>
+      <c r="F42" s="3" t="n">
+        <v>3810365000</v>
+      </c>
+      <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Total Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>1700066000</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>1610767000</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>1566157000</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>1501799000</v>
+      </c>
+      <c r="F43" s="3" t="n">
+        <v>1410138000</v>
+      </c>
+      <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Other Non Current Assets</t>
+        </is>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>225031000</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>185159000</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>191150000</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>158688000</v>
+      </c>
+      <c r="F44" s="3" t="n">
+        <v>160664000</v>
+      </c>
+      <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Non Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>288885000</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>280190000</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>240113000</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>235220000</v>
+      </c>
+      <c r="F45" s="3" t="n">
+        <v>230989000</v>
+      </c>
+      <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Goodwill And Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>370417000</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>372421000</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>374149000</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>372570000</v>
+      </c>
+      <c r="F46" s="3" t="n">
+        <v>376535000</v>
+      </c>
+      <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Other Intangible Assets</t>
+        </is>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>5342000</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>7346000</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>9407000</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>11143000</v>
+      </c>
+      <c r="F47" s="3" t="n">
+        <v>15108000</v>
+      </c>
+      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Goodwill</t>
+        </is>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>365075000</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>365075000</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>364742000</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>361427000</v>
+      </c>
+      <c r="F48" s="3" t="n">
+        <v>361427000</v>
+      </c>
+      <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Net PPE</t>
+        </is>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>815733000</v>
+      </c>
+      <c r="C49" s="3" t="n">
+        <v>772997000</v>
+      </c>
+      <c r="D49" s="3" t="n">
+        <v>760745000</v>
+      </c>
+      <c r="E49" s="3" t="n">
+        <v>735321000</v>
+      </c>
+      <c r="F49" s="3" t="n">
+        <v>641950000</v>
+      </c>
+      <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Accumulated Depreciation</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>-640818000</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>-625656000</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>-608802000</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>-593897000</v>
+      </c>
+      <c r="F50" s="3" t="n">
+        <v>-565647000</v>
+      </c>
+      <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Gross PPE</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>1456551000</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>1398653000</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>1369547000</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>1329218000</v>
+      </c>
+      <c r="F51" s="3" t="n">
+        <v>1207597000</v>
+      </c>
+      <c r="G51" s="3" t="n"/>
+      <c r="H51" s="3" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Leases</t>
+        </is>
+      </c>
+      <c r="B52" s="3" t="n">
+        <v>117664000</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>114510000</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>109499000</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>106761000</v>
+      </c>
+      <c r="F52" s="3" t="n">
+        <v>103456000</v>
+      </c>
+      <c r="G52" s="3" t="n"/>
+      <c r="H52" s="3" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Construction In Progress</t>
+        </is>
+      </c>
+      <c r="B53" s="3" t="n">
+        <v>101824000</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>95301000</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>88526000</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>81111000</v>
+      </c>
+      <c r="F53" s="3" t="n">
+        <v>73135000</v>
+      </c>
+      <c r="G53" s="3" t="n"/>
+      <c r="H53" s="3" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Other Properties</t>
+        </is>
+      </c>
+      <c r="B54" s="3" t="n">
+        <v>696904000</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>685878000</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>689207000</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>682388000</v>
+      </c>
+      <c r="F54" s="3" t="n">
+        <v>600357000</v>
+      </c>
+      <c r="G54" s="3" t="n"/>
+      <c r="H54" s="3" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>Machinery Furniture Equipment</t>
+        </is>
+      </c>
+      <c r="B55" s="3" t="n">
+        <v>540159000</v>
+      </c>
+      <c r="C55" s="3" t="n">
+        <v>502964000</v>
+      </c>
+      <c r="D55" s="3" t="n">
+        <v>482315000</v>
+      </c>
+      <c r="E55" s="3" t="n">
+        <v>458958000</v>
+      </c>
+      <c r="F55" s="3" t="n">
+        <v>430649000</v>
+      </c>
+      <c r="G55" s="3" t="n"/>
+      <c r="H55" s="3" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>Properties</t>
+        </is>
+      </c>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="3" t="n"/>
+      <c r="H56" s="3" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>Current Assets</t>
+        </is>
+      </c>
+      <c r="B57" s="3" t="n">
+        <v>3049881000</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>3063492000</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>2652254000</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>2524738000</v>
+      </c>
+      <c r="F57" s="3" t="n">
+        <v>2400227000</v>
+      </c>
+      <c r="G57" s="3" t="n"/>
+      <c r="H57" s="3" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>Other Current Assets</t>
+        </is>
+      </c>
+      <c r="B58" s="3" t="n">
+        <v>437017000</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>356015000</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>307891000</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>305140000</v>
+      </c>
+      <c r="F58" s="3" t="n">
+        <v>270988000</v>
+      </c>
+      <c r="G58" s="3" t="n"/>
+      <c r="H58" s="3" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>Current Deferred Assets</t>
+        </is>
+      </c>
+      <c r="B59" s="3" t="n">
+        <v>143364000</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>139379000</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>109370000</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>104795000</v>
+      </c>
+      <c r="F59" s="3" t="n">
+        <v>101288000</v>
+      </c>
+      <c r="G59" s="3" t="n"/>
+      <c r="H59" s="3" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>Inventory</t>
+        </is>
+      </c>
+      <c r="B60" s="3" t="n">
+        <v>77940000</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>75935000</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>82421000</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>46812000</v>
+      </c>
+      <c r="F60" s="3" t="n">
+        <v>37548000</v>
+      </c>
+      <c r="G60" s="3" t="n"/>
+      <c r="H60" s="3" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>Finished Goods</t>
+        </is>
+      </c>
+      <c r="B61" s="3" t="n">
+        <v>31820000</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>35965000</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>36391000</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>36685000</v>
+      </c>
+      <c r="F61" s="3" t="n">
+        <v>30247000</v>
+      </c>
+      <c r="G61" s="3" t="n"/>
+      <c r="H61" s="3" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>Raw Materials</t>
+        </is>
+      </c>
+      <c r="B62" s="3" t="n">
+        <v>46120000</v>
+      </c>
+      <c r="C62" s="3" t="n">
+        <v>39970000</v>
+      </c>
+      <c r="D62" s="3" t="n">
+        <v>46030000</v>
+      </c>
+      <c r="E62" s="3" t="n">
+        <v>10127000</v>
+      </c>
+      <c r="F62" s="3" t="n">
+        <v>7301000</v>
+      </c>
+      <c r="G62" s="3" t="n"/>
+      <c r="H62" s="3" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Receivables</t>
+        </is>
+      </c>
+      <c r="B63" s="3" t="n">
+        <v>886811000</v>
+      </c>
+      <c r="C63" s="3" t="n">
+        <v>944844000</v>
+      </c>
+      <c r="D63" s="3" t="n">
+        <v>620959000</v>
+      </c>
+      <c r="E63" s="3" t="n">
+        <v>530481000</v>
+      </c>
+      <c r="F63" s="3" t="n">
+        <v>411319000</v>
+      </c>
+      <c r="G63" s="3" t="n"/>
+      <c r="H63" s="3" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B64" s="3" t="n">
+        <v>886811000</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>944844000</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>620959000</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>530481000</v>
+      </c>
+      <c r="F64" s="3" t="n">
+        <v>411319000</v>
+      </c>
+      <c r="G64" s="3" t="n"/>
+      <c r="H64" s="3" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Allowance For Doubtful Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="n">
+        <v>-203000</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>-203000</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>-204000</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>-509000</v>
+      </c>
+      <c r="F65" s="3" t="n">
+        <v>-959000</v>
+      </c>
+      <c r="G65" s="3" t="n"/>
+      <c r="H65" s="3" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Gross Accounts Receivable</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="n">
+        <v>887014000</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>945047000</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>621163000</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>530990000</v>
+      </c>
+      <c r="F66" s="3" t="n">
+        <v>412278000</v>
+      </c>
+      <c r="G66" s="3" t="n"/>
+      <c r="H66" s="3" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Cash Cash Equivalents And Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="n">
+        <v>1504749000</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>1547319000</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>1531613000</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>1537510000</v>
+      </c>
+      <c r="F67" s="3" t="n">
+        <v>1579084000</v>
+      </c>
+      <c r="G67" s="3" t="n"/>
+      <c r="H67" s="3" t="n"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Other Short Term Investments</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="n">
+        <v>666955000</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>692446000</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>678775000</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>649661000</v>
+      </c>
+      <c r="F68" s="3" t="n">
+        <v>839748000</v>
+      </c>
+      <c r="G68" s="3" t="n"/>
+      <c r="H68" s="3" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Cash And Cash Equivalents</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="n">
+        <v>837794000</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>854873000</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>852838000</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>887849000</v>
+      </c>
+      <c r="F69" s="3" t="n">
+        <v>739336000</v>
+      </c>
+      <c r="G69" s="3" t="n"/>
+      <c r="H69" s="3" t="n"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5426,13 +7640,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G50"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -5442,6 +7656,7 @@
     <col width="16" customWidth="1" min="5" max="5"/>
     <col width="16" customWidth="1" min="6" max="6"/>
     <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5452,30 +7667,35 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>2026-04-30</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>2026-01-31</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>2025-10-31</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>2025-07-31</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>2025-04-30</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>2025-01-31</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>2024-10-31</t>
         </is>
@@ -5488,21 +7708,22 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
+        <v>111750000</v>
+      </c>
+      <c r="C2" s="3" t="n">
         <v>201447000</v>
       </c>
-      <c r="C2" s="3" t="n">
+      <c r="D2" s="3" t="n">
         <v>52574000</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
         <v>150130000</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="F2" s="3" t="n">
         <v>211590000</v>
       </c>
-      <c r="F2" s="3" t="n">
-        <v>152422000</v>
-      </c>
       <c r="G2" s="3" t="n"/>
+      <c r="H2" s="3" t="n"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -5511,21 +7732,22 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
+        <v>-84103000</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>-127201000</v>
       </c>
-      <c r="C3" s="3" t="n">
+      <c r="D3" s="3" t="n">
         <v>-53269000</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
         <v>-42242000</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="F3" s="3" t="n">
         <v>-119936000</v>
       </c>
-      <c r="F3" s="3" t="n">
-        <v>-191978000</v>
-      </c>
       <c r="G3" s="3" t="n"/>
+      <c r="H3" s="3" t="n"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -5534,21 +7756,22 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
+        <v>-612000</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>-92000</v>
       </c>
-      <c r="C4" s="3" t="n">
+      <c r="D4" s="3" t="n">
         <v>-2317000</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
         <v>-100000000</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="F4" s="3" t="n">
         <v>-1125000</v>
       </c>
-      <c r="F4" s="3" t="n">
-        <v>-2397000</v>
-      </c>
       <c r="G4" s="3" t="n"/>
+      <c r="H4" s="3" t="n"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5560,12 +7783,13 @@
       <c r="C5" s="3" t="n"/>
       <c r="D5" s="3" t="n"/>
       <c r="E5" s="3" t="n"/>
-      <c r="F5" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F5" s="3" t="n"/>
       <c r="G5" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H5" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -5574,21 +7798,22 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
+        <v>-68414000</v>
+      </c>
+      <c r="C6" s="3" t="n">
         <v>-66552000</v>
       </c>
-      <c r="C6" s="3" t="n">
+      <c r="D6" s="3" t="n">
         <v>-63419000</v>
       </c>
-      <c r="D6" s="3" t="n">
+      <c r="E6" s="3" t="n">
         <v>-62027000</v>
       </c>
-      <c r="E6" s="3" t="n">
+      <c r="F6" s="3" t="n">
         <v>-72346000</v>
       </c>
-      <c r="F6" s="3" t="n">
-        <v>-56086000</v>
-      </c>
       <c r="G6" s="3" t="n"/>
+      <c r="H6" s="3" t="n"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -5600,18 +7825,19 @@
         <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="3" t="n">
         <v>151000</v>
       </c>
-      <c r="D7" s="3" t="n">
+      <c r="E7" s="3" t="n">
         <v>695000</v>
       </c>
-      <c r="E7" s="3" t="n">
+      <c r="F7" s="3" t="n">
         <v>1427000</v>
       </c>
-      <c r="F7" s="3" t="n">
-        <v>1875000</v>
-      </c>
       <c r="G7" s="3" t="n"/>
+      <c r="H7" s="3" t="n"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -5620,21 +7846,22 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
+        <v>876000</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>7846000</v>
       </c>
-      <c r="C8" s="3" t="n">
+      <c r="D8" s="3" t="n">
         <v>3532000</v>
       </c>
-      <c r="D8" s="3" t="n">
+      <c r="E8" s="3" t="n">
         <v>12868000</v>
       </c>
-      <c r="E8" s="3" t="n">
+      <c r="F8" s="3" t="n">
         <v>8273000</v>
       </c>
-      <c r="F8" s="3" t="n">
-        <v>8555000</v>
-      </c>
       <c r="G8" s="3" t="n"/>
+      <c r="H8" s="3" t="n"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -5643,21 +7870,22 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
+        <v>848661000</v>
+      </c>
+      <c r="C9" s="3" t="n">
         <v>864979000</v>
       </c>
-      <c r="C9" s="3" t="n">
+      <c r="D9" s="3" t="n">
         <v>874113000</v>
       </c>
-      <c r="D9" s="3" t="n">
+      <c r="E9" s="3" t="n">
         <v>909690000</v>
       </c>
-      <c r="E9" s="3" t="n">
+      <c r="F9" s="3" t="n">
         <v>760142000</v>
       </c>
-      <c r="F9" s="3" t="n">
-        <v>737750000</v>
-      </c>
       <c r="G9" s="3" t="n"/>
+      <c r="H9" s="3" t="n"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -5666,21 +7894,22 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
+        <v>864979000</v>
+      </c>
+      <c r="C10" s="3" t="n">
         <v>874113000</v>
       </c>
-      <c r="C10" s="3" t="n">
+      <c r="D10" s="3" t="n">
         <v>909690000</v>
       </c>
-      <c r="D10" s="3" t="n">
+      <c r="E10" s="3" t="n">
         <v>760142000</v>
       </c>
-      <c r="E10" s="3" t="n">
+      <c r="F10" s="3" t="n">
         <v>737750000</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>907335000</v>
-      </c>
       <c r="G10" s="3" t="n"/>
+      <c r="H10" s="3" t="n"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -5689,21 +7918,22 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
+        <v>-16318000</v>
+      </c>
+      <c r="C11" s="3" t="n">
         <v>-9134000</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="D11" s="3" t="n">
         <v>-35577000</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="E11" s="3" t="n">
         <v>149548000</v>
       </c>
-      <c r="E11" s="3" t="n">
+      <c r="F11" s="3" t="n">
         <v>22392000</v>
       </c>
-      <c r="F11" s="3" t="n">
-        <v>-169585000</v>
-      </c>
       <c r="G11" s="3" t="n"/>
+      <c r="H11" s="3" t="n"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -5712,21 +7942,22 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
+        <v>-150988000</v>
+      </c>
+      <c r="C12" s="3" t="n">
         <v>-194821000</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="D12" s="3" t="n">
         <v>-107820000</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="E12" s="3" t="n">
         <v>-192384000</v>
       </c>
-      <c r="E12" s="3" t="n">
+      <c r="F12" s="3" t="n">
         <v>-149762000</v>
       </c>
-      <c r="F12" s="3" t="n">
-        <v>-253398000</v>
-      </c>
       <c r="G12" s="3" t="n"/>
+      <c r="H12" s="3" t="n"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -5735,21 +7966,22 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
+        <v>-150988000</v>
+      </c>
+      <c r="C13" s="3" t="n">
         <v>-194821000</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="D13" s="3" t="n">
         <v>-107820000</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="E13" s="3" t="n">
         <v>-192384000</v>
       </c>
-      <c r="E13" s="3" t="n">
+      <c r="F13" s="3" t="n">
         <v>-149762000</v>
       </c>
-      <c r="F13" s="3" t="n">
-        <v>-253398000</v>
-      </c>
       <c r="G13" s="3" t="n"/>
+      <c r="H13" s="3" t="n"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -5758,21 +7990,22 @@
         </is>
       </c>
       <c r="B14" s="3" t="n">
+        <v>-102920000</v>
+      </c>
+      <c r="C14" s="3" t="n">
         <v>-67704000</v>
       </c>
-      <c r="C14" s="3" t="n">
+      <c r="D14" s="3" t="n">
         <v>-85779000</v>
       </c>
-      <c r="D14" s="3" t="n">
+      <c r="E14" s="3" t="n">
         <v>-58241000</v>
       </c>
-      <c r="E14" s="3" t="n">
+      <c r="F14" s="3" t="n">
         <v>-61300000</v>
       </c>
-      <c r="F14" s="3" t="n">
-        <v>-64996000</v>
-      </c>
       <c r="G14" s="3" t="n"/>
+      <c r="H14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -5781,21 +8014,22 @@
         </is>
       </c>
       <c r="B15" s="3" t="n">
+        <v>36647000</v>
+      </c>
+      <c r="C15" s="3" t="n">
         <v>176000</v>
       </c>
-      <c r="C15" s="3" t="n">
+      <c r="D15" s="3" t="n">
         <v>33545000</v>
       </c>
-      <c r="D15" s="3" t="n">
+      <c r="E15" s="3" t="n">
         <v>8099000</v>
       </c>
-      <c r="E15" s="3" t="n">
+      <c r="F15" s="3" t="n">
         <v>32599000</v>
       </c>
-      <c r="F15" s="3" t="n">
-        <v>5973000</v>
-      </c>
       <c r="G15" s="3" t="n"/>
+      <c r="H15" s="3" t="n"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -5804,21 +8038,22 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
+        <v>-84103000</v>
+      </c>
+      <c r="C16" s="3" t="n">
         <v>-127201000</v>
       </c>
-      <c r="C16" s="3" t="n">
+      <c r="D16" s="3" t="n">
         <v>-53269000</v>
       </c>
-      <c r="D16" s="3" t="n">
+      <c r="E16" s="3" t="n">
         <v>-42242000</v>
       </c>
-      <c r="E16" s="3" t="n">
+      <c r="F16" s="3" t="n">
         <v>-119936000</v>
       </c>
-      <c r="F16" s="3" t="n">
-        <v>-191978000</v>
-      </c>
       <c r="G16" s="3" t="n"/>
+      <c r="H16" s="3" t="n"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -5827,21 +8062,22 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
+        <v>-84103000</v>
+      </c>
+      <c r="C17" s="3" t="n">
         <v>-127201000</v>
       </c>
-      <c r="C17" s="3" t="n">
+      <c r="D17" s="3" t="n">
         <v>-53269000</v>
       </c>
-      <c r="D17" s="3" t="n">
+      <c r="E17" s="3" t="n">
         <v>-42242000</v>
       </c>
-      <c r="E17" s="3" t="n">
+      <c r="F17" s="3" t="n">
         <v>-119936000</v>
       </c>
-      <c r="F17" s="3" t="n">
-        <v>-191978000</v>
-      </c>
       <c r="G17" s="3" t="n"/>
+      <c r="H17" s="3" t="n"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -5850,21 +8086,22 @@
         </is>
       </c>
       <c r="B18" s="3" t="n">
+        <v>-612000</v>
+      </c>
+      <c r="C18" s="3" t="n">
         <v>-92000</v>
       </c>
-      <c r="C18" s="3" t="n">
+      <c r="D18" s="3" t="n">
         <v>-2317000</v>
       </c>
-      <c r="D18" s="3" t="n">
+      <c r="E18" s="3" t="n">
         <v>-100000000</v>
       </c>
-      <c r="E18" s="3" t="n">
+      <c r="F18" s="3" t="n">
         <v>-1125000</v>
       </c>
-      <c r="F18" s="3" t="n">
-        <v>-2397000</v>
-      </c>
       <c r="G18" s="3" t="n"/>
+      <c r="H18" s="3" t="n"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -5873,21 +8110,22 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
+        <v>-612000</v>
+      </c>
+      <c r="C19" s="3" t="n">
         <v>-92000</v>
       </c>
-      <c r="C19" s="3" t="n">
+      <c r="D19" s="3" t="n">
         <v>-2317000</v>
       </c>
-      <c r="D19" s="3" t="n">
+      <c r="E19" s="3" t="n">
         <v>-100000000</v>
       </c>
-      <c r="E19" s="3" t="n">
+      <c r="F19" s="3" t="n">
         <v>-1125000</v>
       </c>
-      <c r="F19" s="3" t="n">
-        <v>-2397000</v>
-      </c>
       <c r="G19" s="3" t="n"/>
+      <c r="H19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -5896,21 +8134,22 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
+        <v>-612000</v>
+      </c>
+      <c r="C20" s="3" t="n">
         <v>-92000</v>
       </c>
-      <c r="C20" s="3" t="n">
+      <c r="D20" s="3" t="n">
         <v>-2317000</v>
       </c>
-      <c r="D20" s="3" t="n">
+      <c r="E20" s="3" t="n">
         <v>-100000000</v>
       </c>
-      <c r="E20" s="3" t="n">
+      <c r="F20" s="3" t="n">
         <v>-1125000</v>
       </c>
-      <c r="F20" s="3" t="n">
-        <v>-2397000</v>
-      </c>
       <c r="G20" s="3" t="n"/>
+      <c r="H20" s="3" t="n"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -5922,12 +8161,13 @@
       <c r="C21" s="3" t="n"/>
       <c r="D21" s="3" t="n"/>
       <c r="E21" s="3" t="n"/>
-      <c r="F21" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="F21" s="3" t="n"/>
       <c r="G21" s="3" t="n">
         <v>0</v>
       </c>
+      <c r="H21" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -5936,21 +8176,22 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
+        <v>-45494000</v>
+      </c>
+      <c r="C22" s="3" t="n">
         <v>-82312000</v>
       </c>
-      <c r="C22" s="3" t="n">
+      <c r="D22" s="3" t="n">
         <v>-43750000</v>
       </c>
-      <c r="D22" s="3" t="n">
+      <c r="E22" s="3" t="n">
         <v>129775000</v>
       </c>
-      <c r="E22" s="3" t="n">
+      <c r="F22" s="3" t="n">
         <v>-111782000</v>
       </c>
-      <c r="F22" s="3" t="n">
-        <v>-124695000</v>
-      </c>
       <c r="G22" s="3" t="n"/>
+      <c r="H22" s="3" t="n"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -5959,21 +8200,22 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
+        <v>-45494000</v>
+      </c>
+      <c r="C23" s="3" t="n">
         <v>-82312000</v>
       </c>
-      <c r="C23" s="3" t="n">
+      <c r="D23" s="3" t="n">
         <v>-43750000</v>
       </c>
-      <c r="D23" s="3" t="n">
+      <c r="E23" s="3" t="n">
         <v>129775000</v>
       </c>
-      <c r="E23" s="3" t="n">
+      <c r="F23" s="3" t="n">
         <v>-111782000</v>
       </c>
-      <c r="F23" s="3" t="n">
-        <v>-124695000</v>
-      </c>
       <c r="G23" s="3" t="n"/>
+      <c r="H23" s="3" t="n"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -5982,21 +8224,22 @@
         </is>
       </c>
       <c r="B24" s="3" t="n">
+        <v>22920000</v>
+      </c>
+      <c r="C24" s="3" t="n">
         <v>-15480000</v>
       </c>
-      <c r="C24" s="3" t="n">
+      <c r="D24" s="3" t="n">
         <v>23932000</v>
       </c>
-      <c r="D24" s="3" t="n">
+      <c r="E24" s="3" t="n">
         <v>191802000</v>
       </c>
-      <c r="E24" s="3" t="n">
+      <c r="F24" s="3" t="n">
         <v>-39436000</v>
       </c>
-      <c r="F24" s="3" t="n">
-        <v>-35779000</v>
-      </c>
       <c r="G24" s="3" t="n"/>
+      <c r="H24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -6005,21 +8248,22 @@
         </is>
       </c>
       <c r="B25" s="3" t="n">
+        <v>135872000</v>
+      </c>
+      <c r="C25" s="3" t="n">
         <v>120270000</v>
       </c>
-      <c r="C25" s="3" t="n">
+      <c r="D25" s="3" t="n">
         <v>93599000</v>
       </c>
-      <c r="D25" s="3" t="n">
+      <c r="E25" s="3" t="n">
         <v>333034000</v>
       </c>
-      <c r="E25" s="3" t="n">
+      <c r="F25" s="3" t="n">
         <v>75460000</v>
       </c>
-      <c r="F25" s="3" t="n">
-        <v>121885000</v>
-      </c>
       <c r="G25" s="3" t="n"/>
+      <c r="H25" s="3" t="n"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -6028,21 +8272,22 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
+        <v>-112952000</v>
+      </c>
+      <c r="C26" s="3" t="n">
         <v>-135750000</v>
       </c>
-      <c r="C26" s="3" t="n">
+      <c r="D26" s="3" t="n">
         <v>-69667000</v>
       </c>
-      <c r="D26" s="3" t="n">
+      <c r="E26" s="3" t="n">
         <v>-141232000</v>
       </c>
-      <c r="E26" s="3" t="n">
+      <c r="F26" s="3" t="n">
         <v>-114896000</v>
       </c>
-      <c r="F26" s="3" t="n">
-        <v>-157664000</v>
-      </c>
       <c r="G26" s="3" t="n"/>
+      <c r="H26" s="3" t="n"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -6050,20 +8295,21 @@
           <t>Net Business Purchase And Sale</t>
         </is>
       </c>
-      <c r="B27" s="3" t="n">
+      <c r="B27" s="3" t="n"/>
+      <c r="C27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C27" s="3" t="n">
+      <c r="D27" s="3" t="n">
         <v>-4263000</v>
-      </c>
-      <c r="D27" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="3" t="n"/>
-      <c r="G27" s="3" t="n">
+      <c r="F27" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="3" t="n"/>
+      <c r="H27" s="3" t="n">
         <v>6081000</v>
       </c>
     </row>
@@ -6073,20 +8319,21 @@
           <t>Purchase Of Business</t>
         </is>
       </c>
-      <c r="B28" s="3" t="n">
+      <c r="B28" s="3" t="n"/>
+      <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="C28" s="3" t="n">
+      <c r="D28" s="3" t="n">
         <v>-4263000</v>
-      </c>
-      <c r="D28" s="3" t="n">
-        <v>0</v>
       </c>
       <c r="E28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="3" t="n"/>
-      <c r="G28" s="3" t="n">
+      <c r="F28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" s="3" t="n"/>
+      <c r="H28" s="3" t="n">
         <v>6081000</v>
       </c>
     </row>
@@ -6097,21 +8344,22 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
+        <v>-68414000</v>
+      </c>
+      <c r="C29" s="3" t="n">
         <v>-66552000</v>
       </c>
-      <c r="C29" s="3" t="n">
+      <c r="D29" s="3" t="n">
         <v>-63419000</v>
       </c>
-      <c r="D29" s="3" t="n">
+      <c r="E29" s="3" t="n">
         <v>-62027000</v>
       </c>
-      <c r="E29" s="3" t="n">
+      <c r="F29" s="3" t="n">
         <v>-72346000</v>
       </c>
-      <c r="F29" s="3" t="n">
-        <v>-56086000</v>
-      </c>
       <c r="G29" s="3" t="n"/>
+      <c r="H29" s="3" t="n"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -6120,21 +8368,22 @@
         </is>
       </c>
       <c r="B30" s="3" t="n">
+        <v>-68414000</v>
+      </c>
+      <c r="C30" s="3" t="n">
         <v>-66552000</v>
       </c>
-      <c r="C30" s="3" t="n">
+      <c r="D30" s="3" t="n">
         <v>-63419000</v>
       </c>
-      <c r="D30" s="3" t="n">
+      <c r="E30" s="3" t="n">
         <v>-62027000</v>
       </c>
-      <c r="E30" s="3" t="n">
+      <c r="F30" s="3" t="n">
         <v>-72346000</v>
       </c>
-      <c r="F30" s="3" t="n">
-        <v>-56086000</v>
-      </c>
       <c r="G30" s="3" t="n"/>
+      <c r="H30" s="3" t="n"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -6143,21 +8392,22 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
+        <v>180164000</v>
+      </c>
+      <c r="C31" s="3" t="n">
         <v>267999000</v>
       </c>
-      <c r="C31" s="3" t="n">
+      <c r="D31" s="3" t="n">
         <v>115993000</v>
       </c>
-      <c r="D31" s="3" t="n">
+      <c r="E31" s="3" t="n">
         <v>212157000</v>
       </c>
-      <c r="E31" s="3" t="n">
+      <c r="F31" s="3" t="n">
         <v>283936000</v>
       </c>
-      <c r="F31" s="3" t="n">
-        <v>208508000</v>
-      </c>
       <c r="G31" s="3" t="n"/>
+      <c r="H31" s="3" t="n"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -6166,21 +8416,22 @@
         </is>
       </c>
       <c r="B32" s="3" t="n">
+        <v>180164000</v>
+      </c>
+      <c r="C32" s="3" t="n">
         <v>267999000</v>
       </c>
-      <c r="C32" s="3" t="n">
+      <c r="D32" s="3" t="n">
         <v>115993000</v>
       </c>
-      <c r="D32" s="3" t="n">
+      <c r="E32" s="3" t="n">
         <v>212157000</v>
       </c>
-      <c r="E32" s="3" t="n">
+      <c r="F32" s="3" t="n">
         <v>283936000</v>
       </c>
-      <c r="F32" s="3" t="n">
-        <v>208508000</v>
-      </c>
       <c r="G32" s="3" t="n"/>
+      <c r="H32" s="3" t="n"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -6189,21 +8440,22 @@
         </is>
       </c>
       <c r="B33" s="3" t="n">
+        <v>-10557000</v>
+      </c>
+      <c r="C33" s="3" t="n">
         <v>-9722000</v>
       </c>
-      <c r="C33" s="3" t="n">
+      <c r="D33" s="3" t="n">
         <v>-117682000</v>
       </c>
-      <c r="D33" s="3" t="n">
+      <c r="E33" s="3" t="n">
         <v>35798000</v>
       </c>
-      <c r="E33" s="3" t="n">
+      <c r="F33" s="3" t="n">
         <v>167181000</v>
       </c>
-      <c r="F33" s="3" t="n">
-        <v>30177000</v>
-      </c>
       <c r="G33" s="3" t="n"/>
+      <c r="H33" s="3" t="n"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -6212,21 +8464,22 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
+        <v>137180000</v>
+      </c>
+      <c r="C34" s="3" t="n">
         <v>197007000</v>
       </c>
-      <c r="C34" s="3" t="n">
+      <c r="D34" s="3" t="n">
         <v>39872000</v>
       </c>
-      <c r="D34" s="3" t="n">
+      <c r="E34" s="3" t="n">
         <v>75781000</v>
       </c>
-      <c r="E34" s="3" t="n">
+      <c r="F34" s="3" t="n">
         <v>28585000</v>
       </c>
-      <c r="F34" s="3" t="n">
-        <v>82736000</v>
-      </c>
       <c r="G34" s="3" t="n"/>
+      <c r="H34" s="3" t="n"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -6235,21 +8488,22 @@
         </is>
       </c>
       <c r="B35" s="3" t="n">
+        <v>-10684000</v>
+      </c>
+      <c r="C35" s="3" t="n">
         <v>-10999000</v>
       </c>
-      <c r="C35" s="3" t="n">
+      <c r="D35" s="3" t="n">
         <v>-12079000</v>
       </c>
-      <c r="D35" s="3" t="n">
+      <c r="E35" s="3" t="n">
         <v>-12275000</v>
       </c>
-      <c r="E35" s="3" t="n">
+      <c r="F35" s="3" t="n">
         <v>-11238000</v>
       </c>
-      <c r="F35" s="3" t="n">
-        <v>-13564000</v>
-      </c>
       <c r="G35" s="3" t="n"/>
+      <c r="H35" s="3" t="n"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -6258,21 +8512,22 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
+        <v>10574000</v>
+      </c>
+      <c r="C36" s="3" t="n">
         <v>10030000</v>
       </c>
-      <c r="C36" s="3" t="n">
+      <c r="D36" s="3" t="n">
         <v>11466000</v>
       </c>
-      <c r="D36" s="3" t="n">
+      <c r="E36" s="3" t="n">
         <v>11561000</v>
       </c>
-      <c r="E36" s="3" t="n">
+      <c r="F36" s="3" t="n">
         <v>8397000</v>
       </c>
-      <c r="F36" s="3" t="n">
-        <v>8251000</v>
-      </c>
       <c r="G36" s="3" t="n"/>
+      <c r="H36" s="3" t="n"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -6281,21 +8536,22 @@
         </is>
       </c>
       <c r="B37" s="3" t="n">
+        <v>-85815000</v>
+      </c>
+      <c r="C37" s="3" t="n">
         <v>151261000</v>
       </c>
-      <c r="C37" s="3" t="n">
+      <c r="D37" s="3" t="n">
         <v>50471000</v>
       </c>
-      <c r="D37" s="3" t="n">
+      <c r="E37" s="3" t="n">
         <v>108790000</v>
       </c>
-      <c r="E37" s="3" t="n">
+      <c r="F37" s="3" t="n">
         <v>-111334000</v>
       </c>
-      <c r="F37" s="3" t="n">
-        <v>111054000</v>
-      </c>
       <c r="G37" s="3" t="n"/>
+      <c r="H37" s="3" t="n"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -6304,21 +8560,22 @@
         </is>
       </c>
       <c r="B38" s="3" t="n">
+        <v>-102069000</v>
+      </c>
+      <c r="C38" s="3" t="n">
         <v>125616000</v>
       </c>
-      <c r="C38" s="3" t="n">
+      <c r="D38" s="3" t="n">
         <v>35268000</v>
       </c>
-      <c r="D38" s="3" t="n">
+      <c r="E38" s="3" t="n">
         <v>84945000</v>
       </c>
-      <c r="E38" s="3" t="n">
+      <c r="F38" s="3" t="n">
         <v>-84343000</v>
       </c>
-      <c r="F38" s="3" t="n">
-        <v>101212000</v>
-      </c>
       <c r="G38" s="3" t="n"/>
+      <c r="H38" s="3" t="n"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -6327,21 +8584,22 @@
         </is>
       </c>
       <c r="B39" s="3" t="n">
+        <v>16254000</v>
+      </c>
+      <c r="C39" s="3" t="n">
         <v>25645000</v>
       </c>
-      <c r="C39" s="3" t="n">
+      <c r="D39" s="3" t="n">
         <v>15203000</v>
       </c>
-      <c r="D39" s="3" t="n">
+      <c r="E39" s="3" t="n">
         <v>23845000</v>
       </c>
-      <c r="E39" s="3" t="n">
+      <c r="F39" s="3" t="n">
         <v>-26991000</v>
       </c>
-      <c r="F39" s="3" t="n">
-        <v>9842000</v>
-      </c>
       <c r="G39" s="3" t="n"/>
+      <c r="H39" s="3" t="n"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -6350,21 +8608,22 @@
         </is>
       </c>
       <c r="B40" s="3" t="n">
+        <v>16254000</v>
+      </c>
+      <c r="C40" s="3" t="n">
         <v>25645000</v>
       </c>
-      <c r="C40" s="3" t="n">
+      <c r="D40" s="3" t="n">
         <v>15203000</v>
       </c>
-      <c r="D40" s="3" t="n">
+      <c r="E40" s="3" t="n">
         <v>23845000</v>
       </c>
-      <c r="E40" s="3" t="n">
+      <c r="F40" s="3" t="n">
         <v>-26991000</v>
       </c>
-      <c r="F40" s="3" t="n">
-        <v>9842000</v>
-      </c>
       <c r="G40" s="3" t="n"/>
+      <c r="H40" s="3" t="n"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -6373,21 +8632,22 @@
         </is>
       </c>
       <c r="B41" s="3" t="n">
+        <v>-117076000</v>
+      </c>
+      <c r="C41" s="3" t="n">
         <v>-39534000</v>
       </c>
-      <c r="C41" s="3" t="n">
+      <c r="D41" s="3" t="n">
         <v>-86928000</v>
       </c>
-      <c r="D41" s="3" t="n">
+      <c r="E41" s="3" t="n">
         <v>-13961000</v>
       </c>
-      <c r="E41" s="3" t="n">
+      <c r="F41" s="3" t="n">
         <v>-19440000</v>
       </c>
-      <c r="F41" s="3" t="n">
-        <v>-56213000</v>
-      </c>
       <c r="G41" s="3" t="n"/>
+      <c r="H41" s="3" t="n"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -6396,21 +8656,22 @@
         </is>
       </c>
       <c r="B42" s="3" t="n">
+        <v>-2768000</v>
+      </c>
+      <c r="C42" s="3" t="n">
         <v>6418000</v>
       </c>
-      <c r="C42" s="3" t="n">
+      <c r="D42" s="3" t="n">
         <v>-29957000</v>
       </c>
-      <c r="D42" s="3" t="n">
+      <c r="E42" s="3" t="n">
         <v>-14937000</v>
       </c>
-      <c r="E42" s="3" t="n">
+      <c r="F42" s="3" t="n">
         <v>2669000</v>
       </c>
-      <c r="F42" s="3" t="n">
-        <v>551000</v>
-      </c>
       <c r="G42" s="3" t="n"/>
+      <c r="H42" s="3" t="n"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -6419,21 +8680,22 @@
         </is>
       </c>
       <c r="B43" s="3" t="n">
+        <v>58032000</v>
+      </c>
+      <c r="C43" s="3" t="n">
         <v>-323905000</v>
       </c>
-      <c r="C43" s="3" t="n">
+      <c r="D43" s="3" t="n">
         <v>-90527000</v>
       </c>
-      <c r="D43" s="3" t="n">
+      <c r="E43" s="3" t="n">
         <v>-119161000</v>
       </c>
-      <c r="E43" s="3" t="n">
+      <c r="F43" s="3" t="n">
         <v>269542000</v>
       </c>
-      <c r="F43" s="3" t="n">
-        <v>-102638000</v>
-      </c>
       <c r="G43" s="3" t="n"/>
+      <c r="H43" s="3" t="n"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -6442,21 +8704,22 @@
         </is>
       </c>
       <c r="B44" s="3" t="n">
+        <v>58032000</v>
+      </c>
+      <c r="C44" s="3" t="n">
         <v>-323905000</v>
       </c>
-      <c r="C44" s="3" t="n">
+      <c r="D44" s="3" t="n">
         <v>-90527000</v>
       </c>
-      <c r="D44" s="3" t="n">
+      <c r="E44" s="3" t="n">
         <v>-119161000</v>
       </c>
-      <c r="E44" s="3" t="n">
+      <c r="F44" s="3" t="n">
         <v>269542000</v>
       </c>
-      <c r="F44" s="3" t="n">
-        <v>-102638000</v>
-      </c>
       <c r="G44" s="3" t="n"/>
+      <c r="H44" s="3" t="n"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -6465,21 +8728,22 @@
         </is>
       </c>
       <c r="B45" s="3" t="n">
+        <v>4381000</v>
+      </c>
+      <c r="C45" s="3" t="n">
         <v>-23846000</v>
       </c>
-      <c r="C45" s="3" t="n">
+      <c r="D45" s="3" t="n">
         <v>3681000</v>
       </c>
-      <c r="D45" s="3" t="n">
+      <c r="E45" s="3" t="n">
         <v>6322000</v>
       </c>
-      <c r="E45" s="3" t="n">
+      <c r="F45" s="3" t="n">
         <v>705000</v>
       </c>
-      <c r="F45" s="3" t="n">
-        <v>3061000</v>
-      </c>
       <c r="G45" s="3" t="n"/>
+      <c r="H45" s="3" t="n"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -6488,21 +8752,22 @@
         </is>
       </c>
       <c r="B46" s="3" t="n">
+        <v>122064000</v>
+      </c>
+      <c r="C46" s="3" t="n">
         <v>133497000</v>
       </c>
-      <c r="C46" s="3" t="n">
+      <c r="D46" s="3" t="n">
         <v>134487000</v>
       </c>
-      <c r="D46" s="3" t="n">
+      <c r="E46" s="3" t="n">
         <v>117393000</v>
       </c>
-      <c r="E46" s="3" t="n">
+      <c r="F46" s="3" t="n">
         <v>96275000</v>
       </c>
-      <c r="F46" s="3" t="n">
-        <v>102350000</v>
-      </c>
       <c r="G46" s="3" t="n"/>
+      <c r="H46" s="3" t="n"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -6510,9 +8775,7 @@
           <t>Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B47" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="B47" s="3" t="n"/>
       <c r="C47" s="3" t="n">
         <v>0</v>
       </c>
@@ -6523,9 +8786,12 @@
         <v>0</v>
       </c>
       <c r="F47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="G47" s="3" t="n">
         <v>1360000</v>
       </c>
-      <c r="G47" s="3" t="n"/>
+      <c r="H47" s="3" t="n"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -6534,21 +8800,22 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
+        <v>40198000</v>
+      </c>
+      <c r="C48" s="3" t="n">
         <v>40332000</v>
       </c>
-      <c r="C48" s="3" t="n">
+      <c r="D48" s="3" t="n">
         <v>37786000</v>
       </c>
-      <c r="D48" s="3" t="n">
+      <c r="E48" s="3" t="n">
         <v>35927000</v>
       </c>
-      <c r="E48" s="3" t="n">
+      <c r="F48" s="3" t="n">
         <v>33770000</v>
       </c>
-      <c r="F48" s="3" t="n">
-        <v>29125000</v>
-      </c>
       <c r="G48" s="3" t="n"/>
+      <c r="H48" s="3" t="n"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -6557,21 +8824,22 @@
         </is>
       </c>
       <c r="B49" s="3" t="n">
+        <v>40198000</v>
+      </c>
+      <c r="C49" s="3" t="n">
         <v>40332000</v>
       </c>
-      <c r="C49" s="3" t="n">
+      <c r="D49" s="3" t="n">
         <v>37786000</v>
       </c>
-      <c r="D49" s="3" t="n">
+      <c r="E49" s="3" t="n">
         <v>35927000</v>
       </c>
-      <c r="E49" s="3" t="n">
+      <c r="F49" s="3" t="n">
         <v>33770000</v>
       </c>
-      <c r="F49" s="3" t="n">
-        <v>29125000</v>
-      </c>
       <c r="G49" s="3" t="n"/>
+      <c r="H49" s="3" t="n"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -6580,28 +8848,29 @@
         </is>
       </c>
       <c r="B50" s="3" t="n">
+        <v>24078000</v>
+      </c>
+      <c r="C50" s="3" t="n">
         <v>100252000</v>
       </c>
-      <c r="C50" s="3" t="n">
+      <c r="D50" s="3" t="n">
         <v>54806000</v>
       </c>
-      <c r="D50" s="3" t="n">
+      <c r="E50" s="3" t="n">
         <v>47118000</v>
       </c>
-      <c r="E50" s="3" t="n">
+      <c r="F50" s="3" t="n">
         <v>-13995000</v>
       </c>
-      <c r="F50" s="3" t="n">
-        <v>42435000</v>
-      </c>
       <c r="G50" s="3" t="n"/>
+      <c r="H50" s="3" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
